--- a/public/volunteer-roster/templates/club-canteen-roster.xlsx
+++ b/public/volunteer-roster/templates/club-canteen-roster.xlsx
@@ -150,17 +150,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Game 1</t>
+          <t xml:space="preserve">Open up</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8:30am – 10:30am</t>
+          <t xml:space="preserve">8:00am – 8:30am</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canteen</t>
+          <t xml:space="preserve">Unlock, float, urn on</t>
         </is>
       </c>
       <c r="D5" s="2"/>
@@ -168,23 +168,31 @@
       <c r="F5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="0"/>
-      <c r="B6" s="0"/>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Canteen</t>
-        </is>
-      </c>
-      <c r="D6" s="0"/>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Game 1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8:30am – 10:30am</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canteen</t>
+        </is>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="0"/>
       <c r="B7" s="0"/>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBQ</t>
+          <t xml:space="preserve">Canteen</t>
         </is>
       </c>
       <c r="D7" s="0"/>
@@ -192,43 +200,43 @@
       <c r="F7" s="0"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="0"/>
+      <c r="B8" s="0"/>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BBQ</t>
+        </is>
+      </c>
+      <c r="D8" s="0"/>
+      <c r="E8" s="0"/>
+      <c r="F8" s="0"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Game 2</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">10:30am – 12:30pm</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Canteen</t>
-        </is>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="0"/>
-      <c r="B9" s="0"/>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Canteen</t>
-        </is>
-      </c>
-      <c r="D9" s="0"/>
-      <c r="E9" s="0"/>
-      <c r="F9" s="0"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canteen</t>
+        </is>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="0"/>
       <c r="B10" s="0"/>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBQ</t>
+          <t xml:space="preserve">Canteen</t>
         </is>
       </c>
       <c r="D10" s="0"/>
@@ -236,43 +244,43 @@
       <c r="F10" s="0"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="0"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BBQ</t>
+        </is>
+      </c>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Game 3</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">12:30pm – 2:30pm</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Canteen</t>
-        </is>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Canteen</t>
-        </is>
-      </c>
-      <c r="D12" s="0"/>
-      <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canteen</t>
+        </is>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
       <c r="B13" s="0"/>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBQ</t>
+          <t xml:space="preserve">Canteen</t>
         </is>
       </c>
       <c r="D13" s="0"/>
@@ -280,43 +288,43 @@
       <c r="F13" s="0"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BBQ</t>
+        </is>
+      </c>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Game 4</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2:30pm – 4:30pm</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Canteen</t>
-        </is>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="0"/>
-      <c r="B15" s="0"/>
-      <c r="C15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Canteen</t>
-        </is>
-      </c>
-      <c r="D15" s="0"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canteen</t>
+        </is>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="0"/>
       <c r="B16" s="0"/>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBQ</t>
+          <t xml:space="preserve">Canteen</t>
         </is>
       </c>
       <c r="D16" s="0"/>
@@ -324,24 +332,16 @@
       <c r="F16" s="0"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open up</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8:00am – 8:30am</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unlock, float, urn on</t>
-        </is>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BBQ</t>
+        </is>
+      </c>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
